--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C98867C-92B0-4EF5-B015-A8018EB269EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27568894-6954-4820-B1A7-FEDE996DB760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="备注类型枚举" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_auto_condition_v8!$A$4:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_auto_condition_v8!$A$4:$K$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -81,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -294,9 +292,6 @@
     <t>释放旋风斩</t>
   </si>
   <si>
-    <t>固定时间释放</t>
-  </si>
-  <si>
     <t>攻击暴击</t>
   </si>
   <si>
@@ -400,10 +395,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>累计攻击次数&gt;=8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>自身生命值&gt;=&lt;最大生命值百万分比</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -428,10 +419,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>累计攻击&gt;=次数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>value_variable</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -480,6 +467,71 @@
   </si>
   <si>
     <t>参数变量id:变化值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒计时结束前，护盾值降低&gt;=&lt;配置值时</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒计时结束前护盾值从&gt;1降低为配置值时</t>
+  </si>
+  <si>
+    <t>倒计时结束前护盾值从&gt;1降低为&lt;=配置值时</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600401:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600201:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计普通攻击&gt;=次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标有冰冻状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标冰冻时—触发释放—伤害</t>
+  </si>
+  <si>
+    <t>使冰冻的目标再次冰冻时—触发释放—伤害</t>
+  </si>
+  <si>
+    <t>目标有燃烧状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>正义光环效果层数&gt;=1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计攻击次数&gt;=12</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -487,7 +539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -934,35 +986,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
@@ -983,16 +1034,16 @@
         <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1003,11 +1054,11 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="F3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1018,18 +1069,18 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>51</v>
@@ -1038,39 +1089,39 @@
         <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
+        <v>1010001</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1">
-        <v>10101</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1082,30 +1133,30 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I5" s="2">
         <v>12</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="K5" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
-        <v>20102</v>
+        <v>2010002</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -1120,7 +1171,7 @@
         <v>53</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2">
         <v>12</v>
@@ -1132,23 +1183,25 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
-        <v>40203</v>
+        <v>3010001</v>
       </c>
       <c r="B7" s="1">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="G7" s="3" t="s">
         <v>54</v>
       </c>
@@ -1163,27 +1216,27 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
-        <v>50101</v>
+        <v>4010003</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="2">
@@ -1193,26 +1246,28 @@
         <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>55010001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
-        <v>60204</v>
+        <v>4020101</v>
       </c>
       <c r="B9" s="1">
-        <v>102</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="D9" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3">
         <v>2</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="2">
@@ -1225,24 +1280,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
-        <v>70101</v>
+        <v>5010001</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>45</v>
@@ -1252,33 +1307,31 @@
         <v>12</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K10" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
-        <v>80106</v>
+        <v>6010102</v>
       </c>
       <c r="B11" s="1">
+        <v>102</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="3">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="3">
-        <v>8</v>
-      </c>
       <c r="E11" s="3">
         <v>1</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="2">
@@ -1291,24 +1344,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
-        <v>90101</v>
+        <v>7010001</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="3">
         <v>1</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>45</v>
@@ -1318,31 +1371,33 @@
         <v>12</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="K12" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
-        <v>100204</v>
+        <v>8010006</v>
       </c>
       <c r="B13" s="1">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="G13" s="3" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="2">
@@ -1351,62 +1406,62 @@
       <c r="J13" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
-        <v>110107</v>
+        <v>9010001</v>
       </c>
       <c r="B14" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="2">
         <v>12</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K14" s="6">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
-        <v>120108</v>
+        <v>10020004</v>
       </c>
       <c r="B15" s="1">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="2">
@@ -1415,31 +1470,29 @@
       <c r="J15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K15" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
-        <v>140109</v>
+        <v>11010007</v>
       </c>
       <c r="B16" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" s="3">
         <v>1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="2">
@@ -1449,63 +1502,63 @@
         <v>0</v>
       </c>
       <c r="K16" s="6">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
-        <v>150109</v>
+        <v>12010008</v>
       </c>
       <c r="B17" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D17" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E17" s="3">
         <v>1</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K17" s="6">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
-        <v>170101</v>
+        <v>14010009</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E18" s="3">
         <v>1</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="2">
@@ -1515,127 +1568,129 @@
         <v>0</v>
       </c>
       <c r="K18" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
-        <v>180101</v>
+        <v>15010009</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="3">
         <v>1</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K19" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>190102</v>
+        <v>17010001</v>
       </c>
       <c r="B20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D20" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3">
         <v>1</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="2">
         <v>12</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K20" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
-        <v>200213</v>
+        <v>18010001</v>
       </c>
       <c r="B21" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D21" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" s="3">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G21" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="2">
         <v>12</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K21" s="6">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
-        <v>210101</v>
+        <v>19010002</v>
       </c>
       <c r="B22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" s="3">
         <v>1</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="2">
@@ -1645,48 +1700,48 @@
         <v>0</v>
       </c>
       <c r="K22" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>10010001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
-        <v>230115</v>
+        <v>21010001</v>
       </c>
       <c r="B23" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" s="3">
         <v>1</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="2">
         <v>12</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K23" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
-        <v>230216</v>
+        <v>23010015</v>
       </c>
       <c r="B24" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>75</v>
@@ -1695,92 +1750,152 @@
         <v>23</v>
       </c>
       <c r="E24" s="3">
-        <v>2</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="G24" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K24" s="6">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
-        <v>240114</v>
+        <v>23020016</v>
       </c>
       <c r="B25" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D25" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="3">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>29</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K25" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
-        <v>240216</v>
+        <v>24010014</v>
       </c>
       <c r="B26" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D26" s="3">
         <v>24</v>
       </c>
       <c r="E26" s="3">
-        <v>2</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="G26" s="3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>24020016</v>
+      </c>
+      <c r="B27" s="1">
+        <v>16</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="3">
+        <v>24</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="2">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6">
         <v>600000</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
-      <c r="L27" s="2"/>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>24020017</v>
+      </c>
+      <c r="B28" s="1">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="3">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="2">
+        <v>23</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K26" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1790,13 +1905,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F74B45-2685-4739-BCB4-4B8546744CDD}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>50</v>
@@ -1806,7 +1921,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1816,7 +1931,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1826,7 +1941,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1836,7 +1951,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1846,7 +1961,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>33</v>
@@ -1854,7 +1969,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1864,7 +1979,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1874,7 +1989,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,7 +1999,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1894,7 +2009,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>34</v>
@@ -1902,7 +2017,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1912,7 +2027,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1922,7 +2037,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1932,7 +2047,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1942,7 +2057,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,7 +2069,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -1966,7 +2081,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1978,7 +2093,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -1990,7 +2105,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -2002,7 +2117,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -2014,7 +2129,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>47</v>
@@ -2024,7 +2139,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2036,7 +2151,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -2048,7 +2163,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -2062,7 +2177,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -2076,7 +2191,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -2096,77 +2211,78 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21444FDA-7D11-468F-8B6C-690382C676F1}">
-  <dimension ref="A5:F23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A5:F28"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1"/>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1"/>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
+      <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1">
         <v>7</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2181,12 +2297,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1"/>
       <c r="E11" s="1">
@@ -2196,108 +2312,127 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C12" s="1"/>
       <c r="E12" s="1">
         <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C13" s="1"/>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
+      <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>12</v>
       </c>
+      <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>14</v>
       </c>
+      <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
         <v>101</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>103</v>
+      </c>
+      <c r="B26" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1">
-        <v>102</v>
-      </c>
-      <c r="B21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1">
-        <v>103</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>104</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1">
-        <v>104</v>
-      </c>
-      <c r="B23" t="s">
-        <v>103</v>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27568894-6954-4820-B1A7-FEDE996DB760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A915E3D5-E6E1-4584-B406-FB9794EF7DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="125">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -532,6 +532,14 @@
   </si>
   <si>
     <t>累计攻击次数&gt;=12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发回血</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在用</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +547,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -596,8 +604,15 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,6 +635,12 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -639,7 +660,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -650,6 +671,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -986,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -1893,6 +1915,38 @@
       </c>
       <c r="K28" s="6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>26010001</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="1">
+        <v>26</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I29" s="1">
+        <v>12</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
